--- a/arcmet_ шаблон.xlsx
+++ b/arcmet_ шаблон.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Arnat\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Проекты\arcmet для запуска\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6302C411-D68E-4197-93D7-0FB31BA850E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1724766-37C2-4841-BFCF-1C1E024A10A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{77260DE7-4101-4562-8B02-5C0164C7FE29}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{77260DE7-4101-4562-8B02-5C0164C7FE29}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="154">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -541,6 +541,22 @@
   </si>
   <si>
     <t>ВОРОНКИ ДЛЯ БАЛКОНОВ И ТЕРРАС</t>
+  </si>
+  <si>
+    <t>01.079</t>
+  </si>
+  <si>
+    <t>01.269</t>
+  </si>
+  <si>
+    <t>Монтажный диаметр, мм: 110,
+Высота выпуска, мм: 470,
+Сырье корпуса: Морозостойкий полипропилен,
+Тип гидроизоляции: Битумно-полимерная,
+Серия: А110Y,
+Высота, мм: 470,
+Тип кровли: Битумно-полимерная,
+Материал корпуса: Морозостойкий полипропилен</t>
   </si>
 </sst>
 </file>
@@ -548,8 +564,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ &quot;₸&quot;_-;\-* #,##0.00\ &quot;₸&quot;_-;_-* &quot;-&quot;??\ &quot;₸&quot;_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₸&quot;_-;\-* #,##0.00\ &quot;₸&quot;_-;_-* &quot;-&quot;??\ &quot;₸&quot;_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
   <fonts count="35" x14ac:knownFonts="1">
     <font>
@@ -1124,12 +1140,12 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="30" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="31" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
@@ -1154,14 +1170,14 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" applyBorder="0">
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1178,13 +1194,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="83">
     <cellStyle name="20% - Accent1" xfId="1" xr:uid="{4C4C0672-0BCC-4108-AF7B-F0CF16919A6D}"/>
@@ -1686,20 +1701,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8696072-4585-4D86-A9C0-5C70B0CFE8B1}">
   <dimension ref="A1:J72"/>
-  <sheetFormatPr defaultRowHeight="40.15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" customWidth="1"/>
-    <col min="2" max="2" width="21.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="30.33203125" customWidth="1"/>
+    <col min="2" max="2" width="21.5546875" customWidth="1"/>
+    <col min="3" max="3" width="54.33203125" customWidth="1"/>
     <col min="4" max="4" width="58" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" customWidth="1"/>
-    <col min="7" max="7" width="20.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" customWidth="1"/>
-    <col min="10" max="10" width="20.5703125" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" customWidth="1"/>
+    <col min="7" max="7" width="20.5546875" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" customWidth="1"/>
+    <col min="10" max="10" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1729,20 +1744,20 @@
       </c>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -1753,40 +1768,46 @@
       <c r="D3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="8" t="e" vm="1">
+      <c r="E3" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="F3" s="8" t="e" vm="2">
+      <c r="F3" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="G3" s="8" t="e" vm="3">
+      <c r="G3" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="I3" s="4">
         <v>600</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="3" t="s">
+        <v>153</v>
+      </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="8" t="e" vm="4">
+      <c r="E4" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>151</v>
+      </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1797,13 +1818,12 @@
       <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="8"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
@@ -1820,7 +1840,7 @@
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>17</v>
       </c>
@@ -1837,7 +1857,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
@@ -1854,7 +1874,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>21</v>
       </c>
@@ -1871,7 +1891,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
@@ -1888,7 +1908,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>25</v>
       </c>
@@ -1905,7 +1925,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>27</v>
       </c>
@@ -1922,7 +1942,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
@@ -1939,7 +1959,7 @@
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>31</v>
       </c>
@@ -1956,7 +1976,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>33</v>
       </c>
@@ -1973,7 +1993,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>35</v>
       </c>
@@ -1990,7 +2010,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
@@ -2007,7 +2027,7 @@
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
@@ -2024,7 +2044,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
@@ -2041,7 +2061,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
@@ -2058,7 +2078,7 @@
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>45</v>
       </c>
@@ -2075,7 +2095,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>47</v>
       </c>
@@ -2092,7 +2112,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>49</v>
       </c>
@@ -2109,7 +2129,7 @@
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>51</v>
       </c>
@@ -2126,7 +2146,7 @@
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>53</v>
       </c>
@@ -2143,7 +2163,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>55</v>
       </c>
@@ -2160,7 +2180,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>57</v>
       </c>
@@ -2177,7 +2197,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>59</v>
       </c>
@@ -2194,7 +2214,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="4"/>
     </row>
-    <row r="29" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>61</v>
       </c>
@@ -2211,7 +2231,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>63</v>
       </c>
@@ -2228,7 +2248,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>65</v>
       </c>
@@ -2245,7 +2265,7 @@
       <c r="H31" s="3"/>
       <c r="I31" s="4"/>
     </row>
-    <row r="32" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>67</v>
       </c>
@@ -2262,7 +2282,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>70</v>
       </c>
@@ -2279,7 +2299,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="4"/>
     </row>
-    <row r="34" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>72</v>
       </c>
@@ -2296,7 +2316,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>74</v>
       </c>
@@ -2313,7 +2333,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>76</v>
       </c>
@@ -2330,20 +2350,20 @@
       <c r="H36" s="3"/>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-    </row>
-    <row r="38" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>78</v>
       </c>
@@ -2360,7 +2380,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>80</v>
       </c>
@@ -2377,7 +2397,7 @@
       <c r="H39" s="3"/>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>82</v>
       </c>
@@ -2394,7 +2414,7 @@
       <c r="H40" s="3"/>
       <c r="I40" s="4"/>
     </row>
-    <row r="41" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>84</v>
       </c>
@@ -2411,7 +2431,7 @@
       <c r="H41" s="3"/>
       <c r="I41" s="4"/>
     </row>
-    <row r="42" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>86</v>
       </c>
@@ -2428,7 +2448,7 @@
       <c r="H42" s="3"/>
       <c r="I42" s="4"/>
     </row>
-    <row r="43" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>88</v>
       </c>
@@ -2445,7 +2465,7 @@
       <c r="H43" s="3"/>
       <c r="I43" s="4"/>
     </row>
-    <row r="44" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>90</v>
       </c>
@@ -2462,7 +2482,7 @@
       <c r="H44" s="3"/>
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>92</v>
       </c>
@@ -2479,7 +2499,7 @@
       <c r="H45" s="3"/>
       <c r="I45" s="4"/>
     </row>
-    <row r="46" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>94</v>
       </c>
@@ -2496,7 +2516,7 @@
       <c r="H46" s="3"/>
       <c r="I46" s="4"/>
     </row>
-    <row r="47" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>96</v>
       </c>
@@ -2513,7 +2533,7 @@
       <c r="H47" s="3"/>
       <c r="I47" s="4"/>
     </row>
-    <row r="48" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>98</v>
       </c>
@@ -2530,7 +2550,7 @@
       <c r="H48" s="3"/>
       <c r="I48" s="4"/>
     </row>
-    <row r="49" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>100</v>
       </c>
@@ -2547,7 +2567,7 @@
       <c r="H49" s="3"/>
       <c r="I49" s="4"/>
     </row>
-    <row r="50" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>102</v>
       </c>
@@ -2564,7 +2584,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="4"/>
     </row>
-    <row r="51" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>104</v>
       </c>
@@ -2581,7 +2601,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="4"/>
     </row>
-    <row r="52" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>106</v>
       </c>
@@ -2598,7 +2618,7 @@
       <c r="H52" s="3"/>
       <c r="I52" s="4"/>
     </row>
-    <row r="53" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>108</v>
       </c>
@@ -2615,7 +2635,7 @@
       <c r="H53" s="3"/>
       <c r="I53" s="4"/>
     </row>
-    <row r="54" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>110</v>
       </c>
@@ -2632,7 +2652,7 @@
       <c r="H54" s="3"/>
       <c r="I54" s="4"/>
     </row>
-    <row r="55" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>112</v>
       </c>
@@ -2649,7 +2669,7 @@
       <c r="H55" s="3"/>
       <c r="I55" s="4"/>
     </row>
-    <row r="56" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>114</v>
       </c>
@@ -2666,7 +2686,7 @@
       <c r="H56" s="3"/>
       <c r="I56" s="4"/>
     </row>
-    <row r="57" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>116</v>
       </c>
@@ -2683,7 +2703,7 @@
       <c r="H57" s="3"/>
       <c r="I57" s="4"/>
     </row>
-    <row r="58" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>118</v>
       </c>
@@ -2700,7 +2720,7 @@
       <c r="H58" s="3"/>
       <c r="I58" s="4"/>
     </row>
-    <row r="59" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>120</v>
       </c>
@@ -2717,7 +2737,7 @@
       <c r="H59" s="3"/>
       <c r="I59" s="4"/>
     </row>
-    <row r="60" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>122</v>
       </c>
@@ -2734,7 +2754,7 @@
       <c r="H60" s="3"/>
       <c r="I60" s="4"/>
     </row>
-    <row r="61" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>124</v>
       </c>
@@ -2751,7 +2771,7 @@
       <c r="H61" s="3"/>
       <c r="I61" s="4"/>
     </row>
-    <row r="62" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>126</v>
       </c>
@@ -2768,7 +2788,7 @@
       <c r="H62" s="3"/>
       <c r="I62" s="4"/>
     </row>
-    <row r="63" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>128</v>
       </c>
@@ -2785,7 +2805,7 @@
       <c r="H63" s="3"/>
       <c r="I63" s="4"/>
     </row>
-    <row r="64" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>130</v>
       </c>
@@ -2802,7 +2822,7 @@
       <c r="H64" s="3"/>
       <c r="I64" s="4"/>
     </row>
-    <row r="65" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>132</v>
       </c>
@@ -2819,7 +2839,7 @@
       <c r="H65" s="3"/>
       <c r="I65" s="4"/>
     </row>
-    <row r="66" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>134</v>
       </c>
@@ -2836,7 +2856,7 @@
       <c r="H66" s="3"/>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>136</v>
       </c>
@@ -2853,7 +2873,7 @@
       <c r="H67" s="3"/>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>138</v>
       </c>
@@ -2870,7 +2890,7 @@
       <c r="H68" s="3"/>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>140</v>
       </c>
@@ -2887,7 +2907,7 @@
       <c r="H69" s="3"/>
       <c r="I69" s="4"/>
     </row>
-    <row r="70" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>142</v>
       </c>
@@ -2904,7 +2924,7 @@
       <c r="H70" s="3"/>
       <c r="I70" s="4"/>
     </row>
-    <row r="71" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>144</v>
       </c>
@@ -2921,7 +2941,7 @@
       <c r="H71" s="3"/>
       <c r="I71" s="4"/>
     </row>
-    <row r="72" spans="1:9" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>146</v>
       </c>

--- a/arcmet_ шаблон.xlsx
+++ b/arcmet_ шаблон.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Проекты\arcmet для запуска\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1724766-37C2-4841-BFCF-1C1E024A10A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB133D47-5CBF-457C-9DD5-5C70AA624236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{77260DE7-4101-4562-8B02-5C0164C7FE29}"/>
   </bookViews>
@@ -88,12 +88,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Номенклатура</t>
-  </si>
-  <si>
-    <t>Ед. изм.</t>
   </si>
   <si>
     <t>Описание</t>
@@ -117,9 +114,6 @@
     <t>Аэратор коньковый FACHMANN с фильтром</t>
   </si>
   <si>
-    <t>шт</t>
-  </si>
-  <si>
     <t>Обеспечивает надежную вентиляцию подкровельного пространства, фильтр защищает от попадания снега, мусора и насекомых.</t>
   </si>
   <si>
@@ -129,409 +123,10 @@
     <t>Предназначен для отвода водяных паров из кровельного пирога, предотвращает образование вздутий на плоской кровле.</t>
   </si>
   <si>
-    <t>Аэратор кровельный А75х375 PP</t>
-  </si>
-  <si>
-    <t>Кровельный вентилятор из ударопрочного полипропилена для просушивания утеплителя плоских кровель.</t>
-  </si>
-  <si>
-    <t>Аэратор кровельный А75х375 PVC</t>
-  </si>
-  <si>
-    <t>Аэратор из ПВХ, идеально совместим с ПВХ-мембранами для герметичного сварного соединения.</t>
-  </si>
-  <si>
-    <t>Аэратор кровельный А75х375 TPO</t>
-  </si>
-  <si>
-    <t>Вентиляционный элемент из ТПО-полимера, предназначен для использования на кровлях из ТПО-мембран.</t>
-  </si>
-  <si>
-    <t>Винт-саморез остроконечный FACHMANN NCRP-4,8x70мм</t>
-  </si>
-  <si>
-    <t>Остроконечный крепеж со стойким антикоррозийным покрытием для фиксации теплоизоляции к профлисту и дереву.</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN NDRP-4,8x100мм</t>
-  </si>
-  <si>
-    <t>Саморез со сверлом для прямого монтажа кровельных систем к металлическому основанию (до 2-3 мм).</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN NDRP-4,8x120 мм</t>
-  </si>
-  <si>
-    <t>Надежный крепежный элемент с буром для толстых слоев теплоизоляции.</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN NDRP-4,8x140 мм</t>
-  </si>
-  <si>
-    <t>Удлиненный кровельный саморез со сверлом для монтажа многослойной изоляции к металлу.</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN NDRP-4,8x160 мм</t>
-  </si>
-  <si>
-    <t>Саморез увеличенной длины с буром для крепления кровельного пирога.</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN NDRP-4,8x60мм</t>
-  </si>
-  <si>
-    <t>Стандартный кровельный саморез со сверлом для монтажа к металлическим конструкциям.</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN NDRP-4,8x70мм</t>
-  </si>
-  <si>
-    <t>Крепежный элемент со сверлом для надежного механического крепления мембран.</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN NDRP-4,8x80мм</t>
-  </si>
-  <si>
-    <t>Саморез с повышенной защитой от коррозии, оснащен буром на конце.</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN NDRP-5,5x35 мм</t>
-  </si>
-  <si>
-    <t>Утолщенный саморез-сверло для высоких ветровых нагрузок и плотных оснований.</t>
-  </si>
-  <si>
-    <t>Винт-саморез сверлоконечный FACHMANN RDRP-4,8х60мм</t>
-  </si>
-  <si>
-    <t>Профессиональный кровельный винт для механического крепления гидроизоляционного слоя.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная V 110X300</t>
-  </si>
-  <si>
-    <t>Универсальная кровельная воронка для организации эффективного водостока с плоских крыш.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная V-TPO 110x450</t>
-  </si>
-  <si>
-    <t>Воронка с заводским фартуком из ТПО для абсолютно герметичной приварки к ТПО-мембранам.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная VM 110x450</t>
-  </si>
-  <si>
-    <t>Модернизированная воронка с увеличенной длиной патрубка для многослойных кровельных систем.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная VM 160x450</t>
-  </si>
-  <si>
-    <t>Воронка увеличенного диаметра (160 мм) для кровель с большой площадью водосбора.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная VO-PVC</t>
-  </si>
-  <si>
-    <t>ПВХ-воронка, обеспечивающая гомогенное соединение с полимерными гидроизоляционными мембранами ПВХ.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная VO-TPO 110x450</t>
-  </si>
-  <si>
-    <t>ТПО-воронка для организации надежного внутреннего водоотвода на полимерных кровлях.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная обогреваемая VMO 110x450</t>
-  </si>
-  <si>
-    <t>Оснащена встроенным термокабелем, предотвращающим замерзание воды в устье воронки зимой.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная обогреваемая VMO 160x450</t>
-  </si>
-  <si>
-    <t>Обогреваемая воронка большого сечения (160 мм) для защиты системы водоотвода от наледи.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная обогреваемая VMO 160x720</t>
-  </si>
-  <si>
-    <t>Обогреваемая воронка с удлиненным патрубком для кровель с толстым слоем утеплителя.</t>
-  </si>
-  <si>
-    <t>Воронка кровельная обогреваемая VO-TPO 110x450</t>
-  </si>
-  <si>
-    <t>Воронка с ТПО-фартуком и системой электрообогрева для круглогодичного водоотвода.</t>
-  </si>
-  <si>
-    <t>Воронка обогреваемая с закладным элементом VMOPro 90x300</t>
-  </si>
-  <si>
-    <t>Профессиональная обогреваемая воронка с закладным кольцом для плотного зажима кровельного ковра.</t>
-  </si>
-  <si>
-    <t>Воронка с закладным элементом VMPro 90x300</t>
-  </si>
-  <si>
-    <t>Воронка с механическим прижимным фланцем для надежной фиксации любых типов гидроизоляции.</t>
-  </si>
-  <si>
-    <t>Герметик полиуретановый FACHMANN PU 35, белый, 600 мл</t>
-  </si>
-  <si>
-    <t>Высокоэластичный белый полиуретановый герметик для заделки швов, фальцев и стыков конструкций.</t>
-  </si>
-  <si>
-    <t>Герметик полиуретановый FACHMANN PU 35, серый, 600 мл</t>
-  </si>
-  <si>
-    <t>Прочный серый герметик, устойчивый к УФ-излучению и деформациям, отлично подходит для кровельных работ.</t>
-  </si>
-  <si>
-    <t>Мембрана ТПО FACHMANN TPO-SR 1.5ММ 2*20М, БЕЛАЯ</t>
-  </si>
-  <si>
-    <t>м2</t>
-  </si>
-  <si>
-    <t>Неармированная белая ТПО мембрана для сложных примыканий, обладает высокой отражающей способностью.</t>
-  </si>
-  <si>
-    <t>Мембрана ТПО FACHMANN TPO-RP 1.2ММ 2*25М, СЕРАЯ</t>
-  </si>
-  <si>
-    <t>Армированная ТПО мембрана (1.2 мм) для создания базового долговечного гидроизоляционного ковра.</t>
-  </si>
-  <si>
-    <t>Мембрана ТПО FACHMANN TPO-RP 1.5ММ 2*20М, СЕРАЯ</t>
-  </si>
-  <si>
-    <t>Утолщенная (1.5 мм) армированная ТПО мембрана с повышенной прочностью и устойчивостью к проколам.</t>
-  </si>
-  <si>
-    <t>Дорожка кровельная FACHMANN Y-образная</t>
-  </si>
-  <si>
-    <t>Противоскользящая пешеходная дорожка для обслуживания оборудования на плоской кровле без риска повредить покрытие.</t>
-  </si>
-  <si>
     <t>Дорожка кровельная ТПО FACHMANN</t>
   </si>
   <si>
     <t>Специализированная пешеходная дорожка из ТПО, легко приваривается к основному кровельному ковру.</t>
-  </si>
-  <si>
-    <t>КОЛПАК ТИАЛ.22002ЛЧ</t>
-  </si>
-  <si>
-    <t>Надежный защитный элемент для кровельных вентиляционных и водосточных систем.</t>
-  </si>
-  <si>
-    <t>Компенсационный патрубок из пластмассы (110)</t>
-  </si>
-  <si>
-    <t>Элемент водосточной системы (110 мм) для компенсации температурных расширений труб.</t>
-  </si>
-  <si>
-    <t>Компенсационный патрубок из пластмассы (160)</t>
-  </si>
-  <si>
-    <t>Патрубок увеличенного диаметра (160 мм) для снятия напряжения в трубопроводах при перепадах температур.</t>
-  </si>
-  <si>
-    <t>Корпус Аэратора А 160 PP</t>
-  </si>
-  <si>
-    <t>Основание вентиляционного аэратора большого сечения для эффективного отвода влаги.</t>
-  </si>
-  <si>
-    <t>Кровельная опора EASY FOOT 300x300 41/21</t>
-  </si>
-  <si>
-    <t>Опорная конструкция для легкого оборудования, кабельных лотков и трубопроводов на мягкой кровле.</t>
-  </si>
-  <si>
-    <t>Кровельная опора SOLID FOOT 350x350</t>
-  </si>
-  <si>
-    <t>Усиленная опора с кронштейном для тяжелого климатического и вентиляционного оборудования.</t>
-  </si>
-  <si>
-    <t>Лист с покрытием ТПО FACHMANN TPO METAL</t>
-  </si>
-  <si>
-    <t>Металл, ламинированный слоем ТПО, для изготовления краевых реек, капельников и сложных примыканий.</t>
-  </si>
-  <si>
-    <t>Муфта с ПВХ/ПП на чугун/сталь 110x100</t>
-  </si>
-  <si>
-    <t>Переходная муфта для герметичного соединения пластиковых водосточных труб с металлическими.</t>
-  </si>
-  <si>
-    <t>Отвод 90 градусов для парапетной воронки 100x100, серый</t>
-  </si>
-  <si>
-    <t>Угловой элемент для плавного поворота сточных вод от парапетной воронки в наружную трубу (серый).</t>
-  </si>
-  <si>
-    <t>Отвод 90 градусов для парапетной воронки 100x100, черный</t>
-  </si>
-  <si>
-    <t>Угловой элемент для плавного поворота сточных вод от парапетной воронки в наружную трубу (черный).</t>
-  </si>
-  <si>
-    <t>Парапетная воронка с листвоуловителем VC-PP 100x100x650</t>
-  </si>
-  <si>
-    <t>Боковая (парапетная) воронка из полипропилена с защитной решеткой от листьев и мусора.</t>
-  </si>
-  <si>
-    <t>Парапетная воронка с листвоуловителем VC-PVC 100x100x650</t>
-  </si>
-  <si>
-    <t>Боковая воронка из ПВХ, обеспечивает идеальную свариваемость с ПВХ-мембранами на парапетах.</t>
-  </si>
-  <si>
-    <t>Парапетная воронка с листвоуловителем VC-TPO 100x100x650</t>
-  </si>
-  <si>
-    <t>Боковой водоотвод из ТПО-полимера для горизонтального вывода воды через парапетную стену.</t>
-  </si>
-  <si>
-    <t>Парапетная воронка с угловым отводом VC-PVC 100x100 ЭКОНОМ</t>
-  </si>
-  <si>
-    <t>Бюджетное решение для бокового водоотвода через парапет на ПВХ-кровлях.</t>
-  </si>
-  <si>
-    <t>Парапетная воронка с угловым отводом VC-PVC 100x100x650</t>
-  </si>
-  <si>
-    <t>Удлиненная парапетная воронка ПВХ в комплекте с угловым отводом для наружного водостока.</t>
-  </si>
-  <si>
-    <t>Патрубок компенсационный ПНД 110</t>
-  </si>
-  <si>
-    <t>Деталь из полиэтилена низкого давления для компенсации линейного удлинения труб 110 мм.</t>
-  </si>
-  <si>
-    <t>Патрубок компенсационный ПНД 160</t>
-  </si>
-  <si>
-    <t>Деталь из полиэтилена низкого давления для труб увеличенного диаметра 160 мм.</t>
-  </si>
-  <si>
-    <t>ПВХ металл, м2</t>
-  </si>
-  <si>
-    <t>Оцинкованная сталь с нанесенным слоем ПВХ для создания жестких примыканий и ветровых планок.</t>
-  </si>
-  <si>
-    <t>Праймер битумный FACHMANN 18 л./16 кг</t>
-  </si>
-  <si>
-    <t>Грунтовочный состав для подготовки бетонных оснований перед наплавлением рулонной гидроизоляции.</t>
-  </si>
-  <si>
-    <t>Праймер битумный FACHMANN 21,5 л./16 кг</t>
-  </si>
-  <si>
-    <t>Битумный праймер в таре увеличенного объема, обеспечивает отличную адгезию кровельных материалов.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х50 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 50 мм) для исключения мостиков холода при креплении теплоизоляции.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х80 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 80 мм) для надежной фиксации кровельного пирога.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х100 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 100 мм), работает в паре с кровельным саморезом.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х120 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 120 мм) для механического крепления теплоизоляционных плит.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х130 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 130 мм), предотвращает повреждение гидроизоляции головкой самореза.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х140 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 140 мм) для средних толщин теплоизоляционного слоя.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х150 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 150 мм) для крепления плоской кровли.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х170 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 170 мм) из ударопрочного пластика.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х180 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 180 мм) для кровель с увеличенным слоем утеплителя.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х200 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 200 мм) для глубокой фиксации в несущем основании.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х220 мм</t>
-  </si>
-  <si>
-    <t>Полимерный дюбель (длина 220 мм) для экстремально толстых кровельных пирогов.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х240 мм</t>
-  </si>
-  <si>
-    <t>Удлиненный полимерный дюбель (длина 240 мм) для систем с высокой теплоизоляцией.</t>
-  </si>
-  <si>
-    <t>Телескопический крепеж FACHMANN 15х260 мм</t>
-  </si>
-  <si>
-    <t>Максимально длинный полимерный дюбель (260 мм) для специального кровельного крепежа.</t>
-  </si>
-  <si>
-    <t>Труба соединительная</t>
-  </si>
-  <si>
-    <t>Универсальный патрубок для соединения элементов внутреннего и внешнего водоотвода.</t>
-  </si>
-  <si>
-    <t>Экструдированная ПВХ воронка</t>
-  </si>
-  <si>
-    <t>Жесткая воронка из экструдированного ПВХ, обладает повышенной стойкостью к деформациям.</t>
   </si>
   <si>
     <t>Характиристики</t>
@@ -558,6 +153,9 @@
 Тип кровли: Битумно-полимерная,
 Материал корпуса: Морозостойкий полипропилен</t>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -819,7 +417,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -927,8 +525,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1089,6 +693,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1177,7 +799,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1199,6 +821,31 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="83">
@@ -1700,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8696072-4585-4D86-A9C0-5C70B0CFE8B1}">
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:M72"/>
   <sheetFormatPr defaultRowHeight="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.33203125" customWidth="1"/>
@@ -1714,15 +1361,15 @@
     <col min="10" max="10" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>148</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1736,274 +1383,213 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E3" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F3" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="4">
+        <v>600</v>
+      </c>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="e" vm="1">
+      <c r="D4" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="F3" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-      <c r="G3" t="e" vm="3">
-        <v>#VALUE!</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="I3" s="4">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" t="e" vm="4">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
+      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
+    <row r="7" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="3" t="s">
-        <v>18</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>21</v>
-      </c>
+      <c r="I8" s="3"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="4"/>
-    </row>
-    <row r="10" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="3" t="s">
-        <v>28</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="4"/>
-    </row>
-    <row r="13" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="3" t="s">
-        <v>30</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>9</v>
-      </c>
+    <row r="15" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
       <c r="C15" s="3"/>
-      <c r="D15" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:10" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>9</v>
-      </c>
+    <row r="16" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
       <c r="C16" s="3"/>
-      <c r="D16" s="3" t="s">
-        <v>36</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
@@ -2011,16 +1597,10 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
       <c r="C17" s="3"/>
-      <c r="D17" s="3" t="s">
-        <v>38</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -2028,16 +1608,10 @@
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
       <c r="C18" s="3"/>
-      <c r="D18" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -2045,16 +1619,10 @@
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
       <c r="C19" s="3"/>
-      <c r="D19" s="3" t="s">
-        <v>42</v>
-      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
@@ -2062,16 +1630,10 @@
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
       <c r="C20" s="3"/>
-      <c r="D20" s="3" t="s">
-        <v>44</v>
-      </c>
+      <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -2079,16 +1641,10 @@
       <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
       <c r="C21" s="3"/>
-      <c r="D21" s="3" t="s">
-        <v>46</v>
-      </c>
+      <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -2096,16 +1652,10 @@
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
       <c r="C22" s="3"/>
-      <c r="D22" s="3" t="s">
-        <v>48</v>
-      </c>
+      <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -2113,16 +1663,10 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="3" t="s">
-        <v>50</v>
-      </c>
+      <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
@@ -2130,16 +1674,10 @@
       <c r="I23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
       <c r="C24" s="3"/>
-      <c r="D24" s="3" t="s">
-        <v>52</v>
-      </c>
+      <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -2147,16 +1685,10 @@
       <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="3"/>
-      <c r="D25" s="3" t="s">
-        <v>54</v>
-      </c>
+      <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -2164,16 +1696,10 @@
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="3" t="s">
-        <v>56</v>
-      </c>
+      <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -2181,16 +1707,10 @@
       <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
       <c r="C27" s="3"/>
-      <c r="D27" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -2198,16 +1718,10 @@
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
       <c r="C28" s="3"/>
-      <c r="D28" s="3" t="s">
-        <v>60</v>
-      </c>
+      <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -2215,16 +1729,10 @@
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
       <c r="C29" s="3"/>
-      <c r="D29" s="3" t="s">
-        <v>62</v>
-      </c>
+      <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -2232,16 +1740,10 @@
       <c r="I29" s="4"/>
     </row>
     <row r="30" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
       <c r="C30" s="3"/>
-      <c r="D30" s="3" t="s">
-        <v>64</v>
-      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -2249,16 +1751,10 @@
       <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
       <c r="C31" s="3"/>
-      <c r="D31" s="3" t="s">
-        <v>66</v>
-      </c>
+      <c r="D31" s="3"/>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -2266,16 +1762,10 @@
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
       <c r="C32" s="3"/>
-      <c r="D32" s="3" t="s">
-        <v>69</v>
-      </c>
+      <c r="D32" s="3"/>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
@@ -2283,16 +1773,10 @@
       <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
       <c r="C33" s="3"/>
-      <c r="D33" s="3" t="s">
-        <v>71</v>
-      </c>
+      <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -2300,16 +1784,10 @@
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
       <c r="C34" s="3"/>
-      <c r="D34" s="3" t="s">
-        <v>73</v>
-      </c>
+      <c r="D34" s="3"/>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -2317,16 +1795,10 @@
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
       <c r="C35" s="3"/>
-      <c r="D35" s="3" t="s">
-        <v>75</v>
-      </c>
+      <c r="D35" s="3"/>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -2334,16 +1806,10 @@
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
       <c r="C36" s="3"/>
-      <c r="D36" s="3" t="s">
-        <v>77</v>
-      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -2351,29 +1817,21 @@
       <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
+      <c r="A37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
     </row>
     <row r="38" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
       <c r="C38" s="3"/>
-      <c r="D38" s="3" t="s">
-        <v>79</v>
-      </c>
+      <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -2381,16 +1839,10 @@
       <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
       <c r="C39" s="3"/>
-      <c r="D39" s="3" t="s">
-        <v>81</v>
-      </c>
+      <c r="D39" s="3"/>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -2398,16 +1850,10 @@
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="D40" s="3"/>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -2415,16 +1861,10 @@
       <c r="I40" s="4"/>
     </row>
     <row r="41" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
       <c r="C41" s="3"/>
-      <c r="D41" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="D41" s="3"/>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -2432,16 +1872,10 @@
       <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
       <c r="C42" s="3"/>
-      <c r="D42" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -2449,16 +1883,10 @@
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
       <c r="C43" s="3"/>
-      <c r="D43" s="3" t="s">
-        <v>89</v>
-      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2466,16 +1894,10 @@
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
       <c r="C44" s="3"/>
-      <c r="D44" s="3" t="s">
-        <v>91</v>
-      </c>
+      <c r="D44" s="3"/>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -2483,16 +1905,10 @@
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
       <c r="C45" s="3"/>
-      <c r="D45" s="3" t="s">
-        <v>93</v>
-      </c>
+      <c r="D45" s="3"/>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -2500,16 +1916,10 @@
       <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
       <c r="C46" s="3"/>
-      <c r="D46" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -2517,16 +1927,10 @@
       <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
       <c r="C47" s="3"/>
-      <c r="D47" s="3" t="s">
-        <v>97</v>
-      </c>
+      <c r="D47" s="3"/>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -2534,16 +1938,10 @@
       <c r="I47" s="4"/>
     </row>
     <row r="48" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
       <c r="C48" s="3"/>
-      <c r="D48" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="D48" s="3"/>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -2551,16 +1949,10 @@
       <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
       <c r="C49" s="3"/>
-      <c r="D49" s="3" t="s">
-        <v>101</v>
-      </c>
+      <c r="D49" s="3"/>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2568,16 +1960,10 @@
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
       <c r="C50" s="3"/>
-      <c r="D50" s="3" t="s">
-        <v>103</v>
-      </c>
+      <c r="D50" s="3"/>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -2585,16 +1971,10 @@
       <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
       <c r="C51" s="3"/>
-      <c r="D51" s="3" t="s">
-        <v>105</v>
-      </c>
+      <c r="D51" s="3"/>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -2602,16 +1982,10 @@
       <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
       <c r="C52" s="3"/>
-      <c r="D52" s="3" t="s">
-        <v>107</v>
-      </c>
+      <c r="D52" s="3"/>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -2619,16 +1993,10 @@
       <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
       <c r="C53" s="3"/>
-      <c r="D53" s="3" t="s">
-        <v>109</v>
-      </c>
+      <c r="D53" s="3"/>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
@@ -2636,16 +2004,10 @@
       <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
       <c r="C54" s="3"/>
-      <c r="D54" s="3" t="s">
-        <v>111</v>
-      </c>
+      <c r="D54" s="3"/>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
@@ -2653,16 +2015,10 @@
       <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>68</v>
-      </c>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
       <c r="C55" s="3"/>
-      <c r="D55" s="3" t="s">
-        <v>113</v>
-      </c>
+      <c r="D55" s="3"/>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
@@ -2670,16 +2026,10 @@
       <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
       <c r="C56" s="3"/>
-      <c r="D56" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
@@ -2687,16 +2037,10 @@
       <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="3" t="s">
-        <v>117</v>
-      </c>
+      <c r="D57" s="3"/>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -2704,16 +2048,10 @@
       <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
       <c r="C58" s="3"/>
-      <c r="D58" s="3" t="s">
-        <v>119</v>
-      </c>
+      <c r="D58" s="3"/>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
@@ -2721,16 +2059,10 @@
       <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
       <c r="C59" s="3"/>
-      <c r="D59" s="3" t="s">
-        <v>121</v>
-      </c>
+      <c r="D59" s="3"/>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
@@ -2738,16 +2070,10 @@
       <c r="I59" s="4"/>
     </row>
     <row r="60" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A60" s="3"/>
+      <c r="B60" s="3"/>
       <c r="C60" s="3"/>
-      <c r="D60" s="3" t="s">
-        <v>123</v>
-      </c>
+      <c r="D60" s="3"/>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
@@ -2755,16 +2081,10 @@
       <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
       <c r="C61" s="3"/>
-      <c r="D61" s="3" t="s">
-        <v>125</v>
-      </c>
+      <c r="D61" s="3"/>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
@@ -2772,16 +2092,10 @@
       <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A62" s="3"/>
+      <c r="B62" s="3"/>
       <c r="C62" s="3"/>
-      <c r="D62" s="3" t="s">
-        <v>127</v>
-      </c>
+      <c r="D62" s="3"/>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
@@ -2789,16 +2103,10 @@
       <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
       <c r="C63" s="3"/>
-      <c r="D63" s="3" t="s">
-        <v>129</v>
-      </c>
+      <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
@@ -2806,16 +2114,10 @@
       <c r="I63" s="4"/>
     </row>
     <row r="64" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A64" s="3"/>
+      <c r="B64" s="3"/>
       <c r="C64" s="3"/>
-      <c r="D64" s="3" t="s">
-        <v>131</v>
-      </c>
+      <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="3"/>
@@ -2823,16 +2125,10 @@
       <c r="I64" s="4"/>
     </row>
     <row r="65" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
       <c r="C65" s="3"/>
-      <c r="D65" s="3" t="s">
-        <v>133</v>
-      </c>
+      <c r="D65" s="3"/>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
       <c r="G65" s="3"/>
@@ -2840,16 +2136,10 @@
       <c r="I65" s="4"/>
     </row>
     <row r="66" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A66" s="3"/>
+      <c r="B66" s="3"/>
       <c r="C66" s="3"/>
-      <c r="D66" s="3" t="s">
-        <v>135</v>
-      </c>
+      <c r="D66" s="3"/>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
@@ -2857,16 +2147,10 @@
       <c r="I66" s="4"/>
     </row>
     <row r="67" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="3" t="s">
-        <v>137</v>
-      </c>
+      <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -2874,16 +2158,10 @@
       <c r="I67" s="4"/>
     </row>
     <row r="68" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A68" s="3"/>
+      <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="3" t="s">
-        <v>139</v>
-      </c>
+      <c r="D68" s="3"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -2891,16 +2169,10 @@
       <c r="I68" s="4"/>
     </row>
     <row r="69" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="D69" s="3"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -2908,16 +2180,10 @@
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A70" s="3"/>
+      <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="3" t="s">
-        <v>143</v>
-      </c>
+      <c r="D70" s="3"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -2925,16 +2191,10 @@
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="3" t="s">
-        <v>145</v>
-      </c>
+      <c r="D71" s="3"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -2942,16 +2202,10 @@
       <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="A72" s="3"/>
+      <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="3" t="s">
-        <v>147</v>
-      </c>
+      <c r="D72" s="3"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -2961,7 +2215,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A5:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/arcmet_ шаблон.xlsx
+++ b/arcmet_ шаблон.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Проекты\arcmet для запуска\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB133D47-5CBF-457C-9DD5-5C70AA624236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91401DC3-3221-403E-80F7-A6D2E69DCC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{77260DE7-4101-4562-8B02-5C0164C7FE29}"/>
   </bookViews>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="4">
+  <futureMetadata name="XLRICHVALUE" count="7">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -69,8 +69,29 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="4">
+  <valueMetadata count="7">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -83,12 +104,21 @@
     <bk>
       <rc t="1" v="3"/>
     </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -156,6 +186,12 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>02.050</t>
+  </si>
+  <si>
+    <t>Материал: ТПО</t>
+  </si>
 </sst>
 </file>
 
@@ -165,7 +201,7 @@
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;₸&quot;_-;\-* #,##0.00\ &quot;₸&quot;_-;_-* &quot;-&quot;??\ &quot;₸&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₽_-;\-* #,##0.00\ _₽_-;_-* &quot;-&quot;??\ _₽_-;_-@_-"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +451,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Proxima Nova Rg"/>
     </font>
   </fonts>
   <fills count="20">
@@ -799,7 +840,7 @@
       <alignment vertical="top"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -847,6 +888,7 @@
     <xf numFmtId="0" fontId="34" fillId="19" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="83">
     <cellStyle name="20% - Accent1" xfId="1" xr:uid="{4C4C0672-0BCC-4108-AF7B-F0CF16919A6D}"/>
@@ -987,7 +1029,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -1008,6 +1050,21 @@
     <v>5</v>
     <v>Аэратор кровельный А110Y 01.079 - Fachmann</v>
   </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+    <v>Дорожка кровельная ТПО FACHMANN Y-образная 02.050 - Fachmann</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+    <v>Дорожка кровельная ТПО FACHMANN Y-образная 02.050 - Fachmann</v>
+  </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+    <v>Дорожка кровельная ТПО FACHMANN Y-образная 02.050 - Fachmann</v>
+  </rv>
 </rvData>
 </file>
 
@@ -1027,6 +1084,9 @@
   <rel r:id="rId2"/>
   <rel r:id="rId3"/>
   <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
 </richValueRels>
 </file>
 
@@ -1348,12 +1408,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8696072-4585-4D86-A9C0-5C70B0CFE8B1}">
   <dimension ref="A1:M72"/>
-  <sheetFormatPr defaultRowHeight="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="40.200000000000003" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.33203125" customWidth="1"/>
     <col min="2" max="2" width="21.5546875" customWidth="1"/>
     <col min="3" max="3" width="54.33203125" customWidth="1"/>
-    <col min="4" max="4" width="58" customWidth="1"/>
+    <col min="4" max="4" width="37.44140625" customWidth="1"/>
     <col min="5" max="5" width="19.6640625" customWidth="1"/>
     <col min="6" max="6" width="21.5546875" customWidth="1"/>
     <col min="7" max="7" width="20.5546875" customWidth="1"/>
@@ -1361,7 +1421,7 @@
     <col min="10" max="10" width="20.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1389,7 +1449,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="5"/>
     </row>
-    <row r="2" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A2" s="10" t="s">
         <v>14</v>
       </c>
@@ -1402,7 +1462,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
@@ -1427,7 +1487,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1448,7 +1508,7 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -1461,22 +1521,32 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="D6" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E6" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="F6" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>20</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1491,7 +1561,7 @@
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
     </row>
-    <row r="8" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1504,7 +1574,7 @@
       <c r="L8" s="16"/>
       <c r="M8" s="15"/>
     </row>
-    <row r="9" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>19</v>
@@ -1519,7 +1589,7 @@
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1530,7 +1600,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1541,7 +1611,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1552,7 +1622,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1563,7 +1633,7 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1574,7 +1644,7 @@
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1585,7 +1655,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1596,7 +1666,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1607,7 +1677,7 @@
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1618,7 +1688,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1629,7 +1699,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1640,7 +1710,7 @@
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1651,7 +1721,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1662,7 +1732,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1673,7 +1743,7 @@
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1684,7 +1754,7 @@
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1695,7 +1765,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1706,7 +1776,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1717,7 +1787,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="4"/>
     </row>
-    <row r="28" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1728,7 +1798,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="4"/>
     </row>
-    <row r="29" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1739,7 +1809,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1750,7 +1820,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1761,7 +1831,7 @@
       <c r="H31" s="3"/>
       <c r="I31" s="4"/>
     </row>
-    <row r="32" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1772,7 +1842,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1783,7 +1853,7 @@
       <c r="H33" s="3"/>
       <c r="I33" s="4"/>
     </row>
-    <row r="34" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1794,7 +1864,7 @@
       <c r="H34" s="3"/>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1805,7 +1875,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1816,7 +1886,7 @@
       <c r="H36" s="3"/>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -1827,7 +1897,7 @@
       <c r="H37" s="9"/>
       <c r="I37" s="9"/>
     </row>
-    <row r="38" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1838,7 +1908,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1849,7 +1919,7 @@
       <c r="H39" s="3"/>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1860,7 +1930,7 @@
       <c r="H40" s="3"/>
       <c r="I40" s="4"/>
     </row>
-    <row r="41" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1871,7 +1941,7 @@
       <c r="H41" s="3"/>
       <c r="I41" s="4"/>
     </row>
-    <row r="42" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -1882,7 +1952,7 @@
       <c r="H42" s="3"/>
       <c r="I42" s="4"/>
     </row>
-    <row r="43" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1893,7 +1963,7 @@
       <c r="H43" s="3"/>
       <c r="I43" s="4"/>
     </row>
-    <row r="44" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1904,7 +1974,7 @@
       <c r="H44" s="3"/>
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1915,7 +1985,7 @@
       <c r="H45" s="3"/>
       <c r="I45" s="4"/>
     </row>
-    <row r="46" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1926,7 +1996,7 @@
       <c r="H46" s="3"/>
       <c r="I46" s="4"/>
     </row>
-    <row r="47" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1937,7 +2007,7 @@
       <c r="H47" s="3"/>
       <c r="I47" s="4"/>
     </row>
-    <row r="48" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1948,7 +2018,7 @@
       <c r="H48" s="3"/>
       <c r="I48" s="4"/>
     </row>
-    <row r="49" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1959,7 +2029,7 @@
       <c r="H49" s="3"/>
       <c r="I49" s="4"/>
     </row>
-    <row r="50" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -1970,7 +2040,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="4"/>
     </row>
-    <row r="51" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1981,7 +2051,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="4"/>
     </row>
-    <row r="52" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1992,7 +2062,7 @@
       <c r="H52" s="3"/>
       <c r="I52" s="4"/>
     </row>
-    <row r="53" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2003,7 +2073,7 @@
       <c r="H53" s="3"/>
       <c r="I53" s="4"/>
     </row>
-    <row r="54" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2014,7 +2084,7 @@
       <c r="H54" s="3"/>
       <c r="I54" s="4"/>
     </row>
-    <row r="55" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2025,7 +2095,7 @@
       <c r="H55" s="3"/>
       <c r="I55" s="4"/>
     </row>
-    <row r="56" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2036,7 +2106,7 @@
       <c r="H56" s="3"/>
       <c r="I56" s="4"/>
     </row>
-    <row r="57" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2047,7 +2117,7 @@
       <c r="H57" s="3"/>
       <c r="I57" s="4"/>
     </row>
-    <row r="58" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2058,7 +2128,7 @@
       <c r="H58" s="3"/>
       <c r="I58" s="4"/>
     </row>
-    <row r="59" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2069,7 +2139,7 @@
       <c r="H59" s="3"/>
       <c r="I59" s="4"/>
     </row>
-    <row r="60" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -2080,7 +2150,7 @@
       <c r="H60" s="3"/>
       <c r="I60" s="4"/>
     </row>
-    <row r="61" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2091,7 +2161,7 @@
       <c r="H61" s="3"/>
       <c r="I61" s="4"/>
     </row>
-    <row r="62" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2102,7 +2172,7 @@
       <c r="H62" s="3"/>
       <c r="I62" s="4"/>
     </row>
-    <row r="63" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -2113,7 +2183,7 @@
       <c r="H63" s="3"/>
       <c r="I63" s="4"/>
     </row>
-    <row r="64" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2124,7 +2194,7 @@
       <c r="H64" s="3"/>
       <c r="I64" s="4"/>
     </row>
-    <row r="65" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2135,7 +2205,7 @@
       <c r="H65" s="3"/>
       <c r="I65" s="4"/>
     </row>
-    <row r="66" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -2146,7 +2216,7 @@
       <c r="H66" s="3"/>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -2157,7 +2227,7 @@
       <c r="H67" s="3"/>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2168,7 +2238,7 @@
       <c r="H68" s="3"/>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -2179,7 +2249,7 @@
       <c r="H69" s="3"/>
       <c r="I69" s="4"/>
     </row>
-    <row r="70" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2190,7 +2260,7 @@
       <c r="H70" s="3"/>
       <c r="I70" s="4"/>
     </row>
-    <row r="71" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2201,7 +2271,7 @@
       <c r="H71" s="3"/>
       <c r="I71" s="4"/>
     </row>
-    <row r="72" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" ht="40.200000000000003" customHeight="1" thickBot="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
